--- a/datatables/datas/游戏模块定义表.xlsx
+++ b/datatables/datas/游戏模块定义表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -35,10 +35,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>display_name</t>
-  </si>
-  <si>
-    <t>path</t>
+    <t>full_name</t>
   </si>
   <si>
     <t>identify_type</t>
@@ -74,10 +71,7 @@
     <t>##</t>
   </si>
   <si>
-    <t>显示名称</t>
-  </si>
-  <si>
-    <t>路径</t>
+    <t>全名称（路径+名称）</t>
   </si>
   <si>
     <t>识别类型</t>
@@ -1314,22 +1308,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.9636363636364" style="3" customWidth="1"/>
-    <col min="4" max="4" width="19.5727272727273" style="3" customWidth="1"/>
-    <col min="5" max="6" width="26.0727272727273" style="3" customWidth="1"/>
-    <col min="7" max="7" width="22.5181818181818" style="3" customWidth="1"/>
-    <col min="8" max="8" width="41.3181818181818" style="3" customWidth="1"/>
-    <col min="9" max="16358" width="9.13636363636364" style="3" customWidth="1"/>
-    <col min="16359" max="16359" width="9.13636363636364" style="3"/>
-    <col min="16360" max="16384" width="9" style="3"/>
+    <col min="3" max="3" width="20.3454545454545" style="3" customWidth="1"/>
+    <col min="4" max="5" width="26.0727272727273" style="3" customWidth="1"/>
+    <col min="6" max="6" width="22.5181818181818" style="3" customWidth="1"/>
+    <col min="7" max="7" width="41.3181818181818" style="3" customWidth="1"/>
+    <col min="8" max="16357" width="9.13636363636364" style="3" customWidth="1"/>
+    <col min="16358" max="16358" width="9.13636363636364" style="3"/>
+    <col min="16359" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1351,39 +1344,33 @@
       <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="14.5" spans="1:7">
+      <c r="A3" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="14.5" spans="1:8">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1391,127 +1378,122 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="6"/>
       <c r="B5" s="7">
         <v>1001</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="4:4">
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="4:4">
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="4:4">
-      <c r="D19" s="9"/>
-    </row>
-    <row r="20" spans="4:4">
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="4:4">
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="4:4">
-      <c r="D22" s="9"/>
-    </row>
-    <row r="23" spans="4:4">
-      <c r="D23" s="9"/>
-    </row>
-    <row r="24" spans="4:4">
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="4:4">
-      <c r="D25" s="9"/>
-    </row>
-    <row r="26" spans="4:4">
-      <c r="D26" s="9"/>
-    </row>
-    <row r="27" spans="4:4">
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="4:4">
-      <c r="D28" s="9"/>
-    </row>
-    <row r="29" spans="4:4">
-      <c r="D29" s="9"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="C7" s="9"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="C8" s="9"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="C9" s="9"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="C11" s="9"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="C13" s="9"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="C16" s="9"/>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="9"/>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="9"/>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="9"/>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="9"/>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="9"/>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="9"/>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="9"/>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" s="9"/>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" s="9"/>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datatables/datas/游戏模块定义表.xlsx
+++ b/datatables/datas/游戏模块定义表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -96,6 +96,162 @@
   </si>
   <si>
     <t>进入游戏内第一个面板中底下的主页</t>
+  </si>
+  <si>
+    <t>主页/元素之力</t>
+  </si>
+  <si>
+    <t>主页-元素之力.png</t>
+  </si>
+  <si>
+    <t>主页/任务</t>
+  </si>
+  <si>
+    <t>主页-任务.png</t>
+  </si>
+  <si>
+    <t>主页/公会</t>
+  </si>
+  <si>
+    <t>主页-公会.png</t>
+  </si>
+  <si>
+    <t>主页/家园</t>
+  </si>
+  <si>
+    <t>主页-家园.png</t>
+  </si>
+  <si>
+    <t>主页/工程学</t>
+  </si>
+  <si>
+    <t>主页-工程学.png</t>
+  </si>
+  <si>
+    <t>主页/兑换商店</t>
+  </si>
+  <si>
+    <t>主页-兑换商店.png</t>
+  </si>
+  <si>
+    <t>主页/泰坦之旅</t>
+  </si>
+  <si>
+    <t>主页-泰坦之旅.png</t>
+  </si>
+  <si>
+    <t>主页/宝石</t>
+  </si>
+  <si>
+    <t>主页-宝石.png</t>
+  </si>
+  <si>
+    <t>主页/维迪卡尔</t>
+  </si>
+  <si>
+    <t>主页-维迪卡尔.png</t>
+  </si>
+  <si>
+    <t>主页/梦境之战</t>
+  </si>
+  <si>
+    <t>主页-梦境之战.png</t>
+  </si>
+  <si>
+    <t>主页/雕文</t>
+  </si>
+  <si>
+    <t>主页-雕文.png</t>
+  </si>
+  <si>
+    <t>主页/家园/大厅</t>
+  </si>
+  <si>
+    <t>主页-家园-大厅.png</t>
+  </si>
+  <si>
+    <t>主页/家园/农场</t>
+  </si>
+  <si>
+    <t>主页-家园-农场.png</t>
+  </si>
+  <si>
+    <t>主页/家园/酒馆</t>
+  </si>
+  <si>
+    <t>主页-家园-酒馆.png</t>
+  </si>
+  <si>
+    <t>主页/家园/炼金实验室</t>
+  </si>
+  <si>
+    <t>主页-家园-炼金实验室.png</t>
+  </si>
+  <si>
+    <t>主页/家园/守护之光</t>
+  </si>
+  <si>
+    <t>主页-家园-守护之光.png</t>
+  </si>
+  <si>
+    <t>主页/家园/探险乐园</t>
+  </si>
+  <si>
+    <t>主页-家园-探险乐园.png</t>
+  </si>
+  <si>
+    <t>主页/家园/交易所</t>
+  </si>
+  <si>
+    <t>主页-家园-交易所.png</t>
+  </si>
+  <si>
+    <t>主页/家园/加工厂</t>
+  </si>
+  <si>
+    <t>主页-家园-加工厂.png</t>
+  </si>
+  <si>
+    <t>主页/家园/驿站</t>
+  </si>
+  <si>
+    <t>主页-家园-驿站.png</t>
+  </si>
+  <si>
+    <t>主页/家园/研究院</t>
+  </si>
+  <si>
+    <t>主页-家园-研究院.png</t>
+  </si>
+  <si>
+    <t>主页/家园/宠物乐园</t>
+  </si>
+  <si>
+    <t>主页-家园-宠物乐园.png</t>
+  </si>
+  <si>
+    <t>主页/家园/永恒之井</t>
+  </si>
+  <si>
+    <t>主页-家园-永恒之井.png</t>
+  </si>
+  <si>
+    <t>主页/元素之力/元素试炼</t>
+  </si>
+  <si>
+    <t>主页-元素之力-元素试炼.png</t>
+  </si>
+  <si>
+    <t>主页/公会/时空乱流</t>
+  </si>
+  <si>
+    <t>主页-公会-时空乱流.png</t>
+  </si>
+  <si>
+    <t>主页/公会/社区</t>
+  </si>
+  <si>
+    <t>主页/公会/公会副本</t>
   </si>
 </sst>
 </file>
@@ -746,7 +902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -763,7 +919,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -772,7 +928,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1308,13 +1473,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.3454545454545" style="3" customWidth="1"/>
-    <col min="4" max="5" width="26.0727272727273" style="3" customWidth="1"/>
+    <col min="3" max="3" width="31.4545454545455" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26.0727272727273" style="3" customWidth="1"/>
+    <col min="5" max="5" width="29.3" style="3" customWidth="1"/>
     <col min="6" max="6" width="22.5181818181818" style="3" customWidth="1"/>
     <col min="7" max="7" width="41.3181818181818" style="3" customWidth="1"/>
     <col min="8" max="16357" width="9.13636363636364" style="3" customWidth="1"/>
@@ -1424,76 +1590,691 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="C6" s="9"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="7">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="C7" s="9"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="C8" s="9"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="7">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="C9" s="9"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="7">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="C10" s="9"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="7">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="C11" s="9"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="7">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="C12" s="9"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="7">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="C13" s="9"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="7">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="C14" s="9"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="7">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="C15" s="9"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="7">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="C16" s="9"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="9"/>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="3:3">
-      <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" s="9"/>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26" s="9"/>
-    </row>
-    <row r="27" spans="3:3">
-      <c r="C27" s="9"/>
-    </row>
-    <row r="28" spans="3:3">
-      <c r="C28" s="9"/>
-    </row>
-    <row r="29" spans="3:3">
-      <c r="C29" s="9"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="7">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7">
+        <v>1015</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7">
+        <v>1016</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="6"/>
+      <c r="B21" s="7">
+        <v>1017</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7">
+        <v>1018</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="6"/>
+      <c r="B23" s="7">
+        <v>1019</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7">
+        <v>1020</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="6"/>
+      <c r="B25" s="7">
+        <v>1021</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="6"/>
+      <c r="B26" s="7">
+        <v>1022</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="6"/>
+      <c r="B27" s="7">
+        <v>1023</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="6"/>
+      <c r="B28" s="7">
+        <v>1024</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="6"/>
+      <c r="B29" s="7">
+        <v>1025</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="6"/>
+      <c r="B30" s="7">
+        <v>1026</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="6"/>
+      <c r="B31" s="7">
+        <v>1027</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="6"/>
+      <c r="B32" s="7">
+        <v>1028</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="11"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="11"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="11"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="11"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="11"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="11"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="11"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="11"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="11"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="11"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="11"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="11"/>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="11"/>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="11"/>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="11"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="11"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="11"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="11"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="11"/>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="11"/>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="11"/>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="11"/>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="11"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="11"/>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="11"/>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="11"/>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="11"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="11"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="11"/>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="11"/>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="11"/>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="11"/>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="11"/>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="11"/>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="11"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="11"/>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="11"/>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="11"/>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="11"/>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="11"/>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="11"/>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="11"/>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="11"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="11"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="11"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="11"/>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="11"/>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="11"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="11"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="11"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="11"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="11"/>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="11"/>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="11"/>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="11"/>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="11"/>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="12"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
